--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpReceiveFlowDiff.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpReceiveFlowDiff.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -58,7 +56,7 @@
     <t>来源单号（平台）</t>
   </si>
   <si>
-    <t>来源单号（ERP）</t>
+    <t>直接调拨单号（ERP）</t>
   </si>
   <si>
     <t>仓库名称（平台）</t>
@@ -124,16 +122,16 @@
     <t>{.bizCode}</t>
   </si>
   <si>
+    <t>{.orderCode}</t>
+  </si>
+  <si>
     <t>{.transferInfoCode}</t>
   </si>
   <si>
-    <t>{.orderCode}</t>
-  </si>
-  <si>
     <t>{.platformWarehouseName}</t>
   </si>
   <si>
-    <t>{.warehouseName}</t>
+    <t>{.erpWarehouseName}</t>
   </si>
   <si>
     <t>{.platformBillDate}</t>
@@ -1112,7 +1110,7 @@
     <col min="7" max="7" width="17.75" customWidth="1"/>
     <col min="8" max="8" width="18.25" customWidth="1"/>
     <col min="9" max="9" width="20.75" customWidth="1"/>
-    <col min="10" max="10" width="16.375" customWidth="1"/>
+    <col min="10" max="10" width="21.125" customWidth="1"/>
     <col min="11" max="11" width="19" customWidth="1"/>
     <col min="12" max="12" width="18.75" customWidth="1"/>
     <col min="13" max="13" width="17.5" customWidth="1"/>
@@ -1282,28 +1280,4 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpReceiveFlowDiff.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpReceiveFlowDiff.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
   <si>
     <t>核对周期</t>
   </si>
@@ -73,13 +73,22 @@
     <t>单据日期（ERP）</t>
   </si>
   <si>
-    <t>SKU*数量（平台）</t>
-  </si>
-  <si>
-    <t>SKU*数量（转换）</t>
-  </si>
-  <si>
-    <t>SKU*数量（ERP）</t>
+    <t>SKU（平台）</t>
+  </si>
+  <si>
+    <t>数量（平台）</t>
+  </si>
+  <si>
+    <t>SKU（转换）</t>
+  </si>
+  <si>
+    <t>数量（转换）</t>
+  </si>
+  <si>
+    <t>SKU（ERP）</t>
+  </si>
+  <si>
+    <t>数量（ERP）</t>
   </si>
   <si>
     <t>差异数量</t>
@@ -142,13 +151,22 @@
     <t>{.billDate}</t>
   </si>
   <si>
-    <t>{.stockSkuQty}</t>
-  </si>
-  <si>
-    <t>{.platformSkuQty}</t>
-  </si>
-  <si>
-    <t>{.skuQty}</t>
+    <t>{.stockSku}</t>
+  </si>
+  <si>
+    <t>{.stockQty}</t>
+  </si>
+  <si>
+    <t>{.platformSkuNo}</t>
+  </si>
+  <si>
+    <t>{.platformQty}</t>
+  </si>
+  <si>
+    <t>{.skuNo}</t>
+  </si>
+  <si>
+    <t>{.qty}</t>
   </si>
   <si>
     <t>{.diffQty}</t>
@@ -1100,7 +1118,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
@@ -1118,18 +1136,18 @@
     <col min="13" max="13" width="17.5" customWidth="1"/>
     <col min="14" max="14" width="16" customWidth="1"/>
     <col min="15" max="15" width="17.125" customWidth="1"/>
-    <col min="16" max="16" width="17.375" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
-    <col min="18" max="18" width="13.125" customWidth="1"/>
-    <col min="19" max="19" width="12.625" customWidth="1"/>
-    <col min="20" max="20" width="15.75" customWidth="1"/>
-    <col min="21" max="21" width="13.125" customWidth="1"/>
-    <col min="22" max="22" width="14.125" customWidth="1"/>
-    <col min="23" max="23" width="15.5" customWidth="1"/>
-    <col min="24" max="24" width="15.875" customWidth="1"/>
+    <col min="16" max="17" width="17.375" customWidth="1"/>
+    <col min="18" max="19" width="18" customWidth="1"/>
+    <col min="20" max="21" width="13.125" customWidth="1"/>
+    <col min="22" max="22" width="12.625" customWidth="1"/>
+    <col min="23" max="23" width="15.75" customWidth="1"/>
+    <col min="24" max="24" width="13.125" customWidth="1"/>
+    <col min="25" max="25" width="14.125" customWidth="1"/>
+    <col min="26" max="26" width="15.5" customWidth="1"/>
+    <col min="27" max="27" width="15.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:27">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1202,79 +1220,97 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:27">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="O2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="P2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="Q2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="R2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="S2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="T2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="U2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="W2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="X2" t="s">
-        <v>46</v>
+        <v>49</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpReceiveFlowDiff.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpReceiveFlowDiff.xlsx
@@ -4,10 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
   <si>
     <t>核对周期</t>
   </si>
@@ -56,7 +58,7 @@
     <t>来源单号（平台）</t>
   </si>
   <si>
-    <t>直接调拨单号（ERP）</t>
+    <t>来源单号（ERP）</t>
   </si>
   <si>
     <t>仓库名称（平台）</t>
@@ -71,13 +73,22 @@
     <t>单据日期（ERP）</t>
   </si>
   <si>
-    <t>SKU*数量（平台）</t>
-  </si>
-  <si>
-    <t>SKU*数量（转换）</t>
-  </si>
-  <si>
-    <t>SKU*数量（ERP）</t>
+    <t>SKU（平台）</t>
+  </si>
+  <si>
+    <t>数量（平台）</t>
+  </si>
+  <si>
+    <t>SKU（转换）</t>
+  </si>
+  <si>
+    <t>数量（转换）</t>
+  </si>
+  <si>
+    <t>SKU（ERP）</t>
+  </si>
+  <si>
+    <t>数量（ERP）</t>
   </si>
   <si>
     <t>差异数量</t>
@@ -122,16 +133,16 @@
     <t>{.bizCode}</t>
   </si>
   <si>
+    <t>{.transferInfoCode}</t>
+  </si>
+  <si>
     <t>{.orderCode}</t>
   </si>
   <si>
-    <t>{.transferInfoCode}</t>
-  </si>
-  <si>
     <t>{.platformWarehouseName}</t>
   </si>
   <si>
-    <t>{.erpWarehouseName}</t>
+    <t>{.warehouseName}</t>
   </si>
   <si>
     <t>{.platformBillDate}</t>
@@ -140,13 +151,22 @@
     <t>{.billDate}</t>
   </si>
   <si>
-    <t>{.stockSkuQty}</t>
-  </si>
-  <si>
-    <t>{.platformSkuQty}</t>
-  </si>
-  <si>
-    <t>{.skuQty}</t>
+    <t>{.stockSku}</t>
+  </si>
+  <si>
+    <t>{.stockQty}</t>
+  </si>
+  <si>
+    <t>{.platformSkuNo}</t>
+  </si>
+  <si>
+    <t>{.platformQty}</t>
+  </si>
+  <si>
+    <t>{.skuNo}</t>
+  </si>
+  <si>
+    <t>{.qty}</t>
   </si>
   <si>
     <t>{.diffQty}</t>
@@ -1098,7 +1118,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
@@ -1110,24 +1130,24 @@
     <col min="7" max="7" width="17.75" customWidth="1"/>
     <col min="8" max="8" width="18.25" customWidth="1"/>
     <col min="9" max="9" width="20.75" customWidth="1"/>
-    <col min="10" max="10" width="21.125" customWidth="1"/>
+    <col min="10" max="10" width="16.375" customWidth="1"/>
     <col min="11" max="11" width="19" customWidth="1"/>
     <col min="12" max="12" width="18.75" customWidth="1"/>
     <col min="13" max="13" width="17.5" customWidth="1"/>
     <col min="14" max="14" width="16" customWidth="1"/>
     <col min="15" max="15" width="17.125" customWidth="1"/>
-    <col min="16" max="16" width="17.375" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
-    <col min="18" max="18" width="13.125" customWidth="1"/>
-    <col min="19" max="19" width="12.625" customWidth="1"/>
-    <col min="20" max="20" width="15.75" customWidth="1"/>
-    <col min="21" max="21" width="13.125" customWidth="1"/>
-    <col min="22" max="22" width="14.125" customWidth="1"/>
-    <col min="23" max="23" width="15.5" customWidth="1"/>
-    <col min="24" max="24" width="15.875" customWidth="1"/>
+    <col min="16" max="17" width="17.375" customWidth="1"/>
+    <col min="18" max="19" width="18" customWidth="1"/>
+    <col min="20" max="21" width="13.125" customWidth="1"/>
+    <col min="22" max="22" width="12.625" customWidth="1"/>
+    <col min="23" max="23" width="15.75" customWidth="1"/>
+    <col min="24" max="24" width="13.125" customWidth="1"/>
+    <col min="25" max="25" width="14.125" customWidth="1"/>
+    <col min="26" max="26" width="15.5" customWidth="1"/>
+    <col min="27" max="27" width="15.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:27">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1200,79 +1220,97 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:27">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="O2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="P2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="Q2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="R2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="S2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="T2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="U2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="W2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="X2" t="s">
-        <v>46</v>
+        <v>49</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1280,4 +1318,28 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpReceiveFlowDiff.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpReceiveFlowDiff.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="54">
   <si>
     <t>核对周期</t>
   </si>
@@ -58,6 +58,9 @@
     <t>来源单号（平台）</t>
   </si>
   <si>
+    <t>直接调拨单号（ERP）</t>
+  </si>
+  <si>
     <t>来源单号（ERP）</t>
   </si>
   <si>
@@ -133,16 +136,16 @@
     <t>{.bizCode}</t>
   </si>
   <si>
+    <t>{.orderCode}</t>
+  </si>
+  <si>
     <t>{.transferInfoCode}</t>
   </si>
   <si>
-    <t>{.orderCode}</t>
-  </si>
-  <si>
     <t>{.platformWarehouseName}</t>
   </si>
   <si>
-    <t>{.warehouseName}</t>
+    <t>{.erpWarehouseName}</t>
   </si>
   <si>
     <t>{.platformBillDate}</t>
@@ -200,13 +203,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -547,12 +556,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -673,138 +697,141 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1118,7 +1145,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
@@ -1130,24 +1157,24 @@
     <col min="7" max="7" width="17.75" customWidth="1"/>
     <col min="8" max="8" width="18.25" customWidth="1"/>
     <col min="9" max="9" width="20.75" customWidth="1"/>
-    <col min="10" max="10" width="16.375" customWidth="1"/>
-    <col min="11" max="11" width="19" customWidth="1"/>
-    <col min="12" max="12" width="18.75" customWidth="1"/>
-    <col min="13" max="13" width="17.5" customWidth="1"/>
-    <col min="14" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="17.125" customWidth="1"/>
-    <col min="16" max="17" width="17.375" customWidth="1"/>
-    <col min="18" max="19" width="18" customWidth="1"/>
-    <col min="20" max="21" width="13.125" customWidth="1"/>
-    <col min="22" max="22" width="12.625" customWidth="1"/>
-    <col min="23" max="23" width="15.75" customWidth="1"/>
-    <col min="24" max="24" width="13.125" customWidth="1"/>
-    <col min="25" max="25" width="14.125" customWidth="1"/>
-    <col min="26" max="26" width="15.5" customWidth="1"/>
-    <col min="27" max="27" width="15.875" customWidth="1"/>
+    <col min="10" max="11" width="16.375" customWidth="1"/>
+    <col min="12" max="12" width="19" customWidth="1"/>
+    <col min="13" max="13" width="18.75" customWidth="1"/>
+    <col min="14" max="14" width="17.5" customWidth="1"/>
+    <col min="15" max="15" width="16" customWidth="1"/>
+    <col min="16" max="16" width="17.125" customWidth="1"/>
+    <col min="17" max="18" width="17.375" customWidth="1"/>
+    <col min="19" max="20" width="18" customWidth="1"/>
+    <col min="21" max="22" width="13.125" customWidth="1"/>
+    <col min="23" max="23" width="12.625" customWidth="1"/>
+    <col min="24" max="24" width="15.75" customWidth="1"/>
+    <col min="25" max="25" width="13.125" customWidth="1"/>
+    <col min="26" max="26" width="14.125" customWidth="1"/>
+    <col min="27" max="27" width="15.5" customWidth="1"/>
+    <col min="28" max="28" width="15.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:28">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1229,45 +1256,48 @@
       <c r="AA1" t="s">
         <v>26</v>
       </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" ht="14.25" spans="1:28">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H2" t="s">
         <v>34</v>
       </c>
+      <c r="H2" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="I2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" t="s">
         <v>35</v>
-      </c>
-      <c r="K2" t="s">
-        <v>36</v>
       </c>
       <c r="L2" t="s">
         <v>37</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="1" t="s">
         <v>38</v>
       </c>
       <c r="N2" t="s">
@@ -1311,6 +1341,9 @@
       </c>
       <c r="AA2" t="s">
         <v>52</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
